--- a/order_forms/011_textbook_order_form--order_forms.xlsx
+++ b/order_forms/011_textbook_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -998,12 +998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>order_notes</t>
+          <t>order_notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Order Notes</t>
+          <t>Order Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>order_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Order Date</t>
+          <t>Order Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>book_title</t>
+          <t>book_title_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Book Title</t>
+          <t>Book Title 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>order_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Order Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,7 +1189,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1418,7 +1418,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
